--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gateo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E1CBE2-8214-4DB2-86CC-6A0CFB9C3C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F58257D9-1C49-43C2-830C-18A545405715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-7260" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-29055" yWindow="6660" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026年5月_勤務表_完全版" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="186">
   <si>
     <t>2026年5月 勤務表</t>
   </si>
@@ -731,6 +731,65 @@
   </si>
   <si>
     <t>〇 夜勤×</t>
+  </si>
+  <si>
+    <t>けが災害</t>
+    <rPh sb="2" eb="4">
+      <t>サイガイ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>ACS</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>小児</t>
+    <rPh sb="0" eb="2">
+      <t>ショウニ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>消化器</t>
+    <rPh sb="0" eb="3">
+      <t>ショウカキ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>呼吸循環器
+精神</t>
+    <rPh sb="0" eb="2">
+      <t>コキュウ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ジュンカンキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>セイシン</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>精神</t>
+    <rPh sb="0" eb="2">
+      <t>セイシン</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>二次輪番</t>
+    <rPh sb="0" eb="1">
+      <t>ニ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>リンバン</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
   </si>
 </sst>
 </file>
@@ -1170,7 +1229,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF27"/>
+  <dimension ref="A1:AF28"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1406,208 +1465,174 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="O4" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="P4" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="R4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="S4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="T4" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="U4" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="V4" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="W4" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="X4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z4" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="AA4" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB4" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="AC4" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="AD4" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="AE4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="AF4" s="3" t="s">
-        <v>156</v>
+    <row r="4" spans="1:32" ht="54.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="G4" s="5"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="X4" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y4" s="5"/>
+      <c r="Z4" s="4"/>
+      <c r="AA4" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="AB4" s="4"/>
+      <c r="AC4" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="AD4" s="4"/>
+      <c r="AE4" s="5"/>
+      <c r="AF4" s="5" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>13</v>
+        <v>160</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="O5" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="P5" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="R5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="S5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="T5" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="U5" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="V5" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="W5" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="X5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z5" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="AA5" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="AB5" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="AC5" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="AD5" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="AE5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF5" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="O5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="P5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="R5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="S5" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="T5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="U5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="V5" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="W5" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="X5" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="Y5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="AA5" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="AB5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="AC5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="AE5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="AF5" s="3" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>13</v>
@@ -1616,301 +1641,301 @@
         <v>13</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="L6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="6" t="s">
+      <c r="M6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="N6" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="O6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="P6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="S6" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="T6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="L6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="N6" s="6" t="s">
+      <c r="U6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="V6" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="W6" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="X6" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="P6" s="6" t="s">
+      <c r="Z6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA6" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="AB6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="Q6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="R6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="S6" s="6" t="s">
+      <c r="AC6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="T6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="U6" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="V6" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="W6" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="X6" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="Y6" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="Z6" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="AA6" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="AB6" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="AC6" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD6" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="AE6" s="3" t="s">
-        <v>156</v>
+        <v>12</v>
       </c>
       <c r="AF6" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="H7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="K7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I7" s="6" t="s">
+      <c r="L7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K7" s="3" t="s">
+      <c r="O7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="P7" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="S7" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="T7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="U7" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="V7" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="W7" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="X7" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="M7" s="6" t="s">
+      <c r="Y7" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="N7" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="O7" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="P7" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="R7" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="S7" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="T7" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="U7" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="V7" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="W7" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="X7" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="Y7" s="3" t="s">
-        <v>170</v>
-      </c>
       <c r="Z7" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AA7" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AB7" s="6" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="AC7" s="6" t="s">
-        <v>170</v>
+        <v>11</v>
       </c>
       <c r="AD7" s="6" t="s">
-        <v>170</v>
+        <v>12</v>
       </c>
       <c r="AE7" s="3" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="AF7" s="3" t="s">
-        <v>170</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="F8" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>155</v>
+        <v>13</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>155</v>
+        <v>11</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>171</v>
+        <v>12</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>12</v>
+        <v>156</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>12</v>
+        <v>170</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="S8" s="6" t="s">
-        <v>13</v>
+        <v>170</v>
       </c>
       <c r="T8" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="U8" s="6" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="V8" s="6" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="W8" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="X8" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="Y8" s="3" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="Z8" s="6" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="AA8" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AB8" s="6" t="s">
-        <v>12</v>
+        <v>170</v>
       </c>
       <c r="AC8" s="6" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="AD8" s="6" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="AE8" s="3" t="s">
-        <v>13</v>
+        <v>170</v>
       </c>
       <c r="AF8" s="3" t="s">
-        <v>13</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>11</v>
+        <v>155</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>13</v>
@@ -1919,721 +1944,755 @@
         <v>13</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>11</v>
+        <v>155</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>12</v>
+        <v>155</v>
       </c>
       <c r="J9" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L9" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>155</v>
-      </c>
       <c r="M9" s="6" t="s">
-        <v>13</v>
+        <v>171</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>175</v>
+        <v>12</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>13</v>
+        <v>156</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>13</v>
+        <v>156</v>
       </c>
       <c r="S9" s="6" t="s">
-        <v>155</v>
+        <v>13</v>
       </c>
       <c r="T9" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="U9" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="V9" s="6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="W9" s="6" t="s">
-        <v>12</v>
+        <v>171</v>
       </c>
       <c r="X9" s="3" t="s">
-        <v>11</v>
+        <v>174</v>
       </c>
       <c r="Y9" s="3" t="s">
-        <v>12</v>
+        <v>155</v>
       </c>
       <c r="Z9" s="6" t="s">
-        <v>11</v>
+        <v>156</v>
       </c>
       <c r="AA9" s="6" t="s">
-        <v>12</v>
+        <v>171</v>
       </c>
       <c r="AB9" s="6" t="s">
-        <v>155</v>
+        <v>12</v>
       </c>
       <c r="AC9" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AD9" s="6" t="s">
-        <v>13</v>
+        <v>156</v>
       </c>
       <c r="AE9" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AF9" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>13</v>
+        <v>155</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>154</v>
+        <v>13</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>20</v>
+        <v>155</v>
       </c>
       <c r="L10" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="O10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="P10" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q10" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="M10" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="N10" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="O10" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="P10" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="R10" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="S10" s="6" t="s">
-        <v>12</v>
+        <v>155</v>
       </c>
       <c r="T10" s="6" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="U10" s="6" t="s">
-        <v>12</v>
+        <v>155</v>
       </c>
       <c r="V10" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="W10" s="6" t="s">
-        <v>157</v>
+        <v>12</v>
       </c>
       <c r="X10" s="3" t="s">
-        <v>155</v>
+        <v>11</v>
       </c>
       <c r="Y10" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="Z10" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA10" s="6" t="s">
-        <v>155</v>
+        <v>12</v>
       </c>
       <c r="AB10" s="6" t="s">
-        <v>13</v>
+        <v>155</v>
       </c>
       <c r="AC10" s="6" t="s">
         <v>155</v>
       </c>
       <c r="AD10" s="6" t="s">
-        <v>155</v>
+        <v>13</v>
       </c>
       <c r="AE10" s="3" t="s">
-        <v>155</v>
+        <v>11</v>
       </c>
       <c r="AF10" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>155</v>
-      </c>
       <c r="F11" s="3" t="s">
-        <v>155</v>
+        <v>12</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>13</v>
+        <v>154</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>155</v>
+        <v>12</v>
       </c>
       <c r="I11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="L11" s="6" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="M11" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="O11" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="P11" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="R11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="N11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="O11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="P11" s="6" t="s">
+      <c r="S11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="T11" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="U11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="V11" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="W11" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="X11" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="Q11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="R11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="S11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="T11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="U11" s="6" t="s">
+      <c r="Z11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA11" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="AB11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AC11" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="AD11" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="AE11" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="AF11" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="V11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="W11" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="X11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z11" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="AA11" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="AB11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="AC11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD11" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="AE11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="AF11" s="3" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="I12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H12" s="6" t="s">
+      <c r="J12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="M12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="I12" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="J12" s="3" t="s">
+      <c r="N12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="O12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="P12" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="S12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="T12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="U12" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="V12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="W12" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="X12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z12" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="AA12" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L12" s="6" t="s">
+      <c r="AB12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="M12" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="O12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="P12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="S12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="T12" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="U12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="V12" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="W12" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="X12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y12" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z12" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA12" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB12" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="AC12" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD12" s="6" t="s">
-        <v>174</v>
-      </c>
       <c r="AE12" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF12" s="3" t="s">
-        <v>13</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>12</v>
+        <v>155</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="H13" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="I13" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L13" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="L13" s="6" t="s">
+      <c r="M13" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="O13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="P13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="S13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="T13" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="U13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="V13" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="M13" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="N13" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="O13" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="P13" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q13" s="3" t="s">
+      <c r="W13" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="R13" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="S13" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="T13" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="U13" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="V13" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="W13" s="6" t="s">
-        <v>155</v>
-      </c>
       <c r="X13" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="Z13" s="6" t="s">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="AA13" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AB13" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="AC13" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="AC13" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="AD13" s="6" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="AE13" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AF13" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
+        <v>23</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="O14" s="6" t="s">
-        <v>25</v>
+        <v>155</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="6"/>
+        <v>13</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="S14" s="6" t="s">
+        <v>154</v>
+      </c>
       <c r="T14" s="6" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="U14" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="V14" s="6"/>
-      <c r="W14" s="6"/>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="3"/>
-      <c r="Z14" s="6"/>
-      <c r="AA14" s="6"/>
-      <c r="AB14" s="6"/>
-      <c r="AC14" s="6"/>
-      <c r="AD14" s="6"/>
-      <c r="AE14" s="3"/>
-      <c r="AF14" s="3"/>
+        <v>155</v>
+      </c>
+      <c r="V14" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="W14" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z14" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="AA14" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB14" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC14" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD14" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="15" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="P15" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
+      <c r="S15" s="6"/>
+      <c r="T15" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="U15" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="V15" s="6"/>
+      <c r="W15" s="6"/>
+      <c r="X15" s="3"/>
+      <c r="Y15" s="3"/>
+      <c r="Z15" s="6"/>
+      <c r="AA15" s="6"/>
+      <c r="AB15" s="6"/>
+      <c r="AC15" s="6"/>
+      <c r="AD15" s="6"/>
+      <c r="AE15" s="3"/>
+      <c r="AF15" s="3"/>
+    </row>
+    <row r="16" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B16" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E16" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F16" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G16" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="H16" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I15" s="6" t="s">
+      <c r="I16" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="K15" s="3" t="s">
+      <c r="K16" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="L15" s="6" t="s">
+      <c r="L16" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M15" s="6" t="s">
+      <c r="M16" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="N15" s="6" t="s">
+      <c r="N16" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="O15" s="6" t="s">
+      <c r="O16" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="P15" s="6" t="s">
+      <c r="P16" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="Q15" s="3" t="s">
+      <c r="Q16" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="R15" s="3" t="s">
+      <c r="R16" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="S15" s="6" t="s">
+      <c r="S16" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="T15" s="6" t="s">
+      <c r="T16" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="U15" s="6" t="s">
+      <c r="U16" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="V15" s="6" t="s">
+      <c r="V16" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="W15" s="6" t="s">
+      <c r="W16" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="X15" s="3" t="s">
+      <c r="X16" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="Y15" s="3" t="s">
+      <c r="Y16" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="Z15" s="3" t="s">
+      <c r="Z16" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="AA15" s="6" t="s">
+      <c r="AA16" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="AB15" s="6" t="s">
+      <c r="AB16" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="AC15" s="6" t="s">
+      <c r="AC16" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="AD15" s="6" t="s">
+      <c r="AD16" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="AE15" s="3" t="s">
+      <c r="AE16" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AF15" s="3" t="s">
+      <c r="AF16" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="17" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="12" t="s">
+    <row r="17" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="18" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
-      <c r="N17" s="13"/>
-      <c r="O17" s="13"/>
-      <c r="P17" s="13"/>
-      <c r="Q17" s="13"/>
-      <c r="R17" s="13"/>
-      <c r="S17" s="13"/>
-      <c r="T17" s="13"/>
-      <c r="U17" s="13"/>
-      <c r="V17" s="13"/>
-      <c r="W17" s="13"/>
-      <c r="X17" s="13"/>
-      <c r="Y17" s="13"/>
-      <c r="Z17" s="13"/>
-      <c r="AA17" s="13"/>
-      <c r="AB17" s="13"/>
-      <c r="AC17" s="13"/>
-      <c r="AD17" s="13"/>
-      <c r="AE17" s="13"/>
-      <c r="AF17" s="13"/>
-    </row>
-    <row r="18" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K18" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="R18" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="S18" s="8"/>
-      <c r="T18" s="8"/>
-      <c r="U18" s="8"/>
-      <c r="V18" s="8"/>
-      <c r="W18" s="8"/>
-      <c r="X18" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y18" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="Z18" s="8"/>
-      <c r="AA18" s="8"/>
-      <c r="AB18" s="8"/>
-      <c r="AC18" s="8"/>
-      <c r="AD18" s="8"/>
-      <c r="AE18" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="AF18" s="9" t="s">
-        <v>37</v>
-      </c>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="13"/>
+      <c r="S18" s="13"/>
+      <c r="T18" s="13"/>
+      <c r="U18" s="13"/>
+      <c r="V18" s="13"/>
+      <c r="W18" s="13"/>
+      <c r="X18" s="13"/>
+      <c r="Y18" s="13"/>
+      <c r="Z18" s="13"/>
+      <c r="AA18" s="13"/>
+      <c r="AB18" s="13"/>
+      <c r="AC18" s="13"/>
+      <c r="AD18" s="13"/>
+      <c r="AE18" s="13"/>
+      <c r="AF18" s="13"/>
     </row>
     <row r="19" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>41</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B19" s="8"/>
       <c r="C19" s="9" t="s">
         <v>37</v>
       </c>
@@ -2649,75 +2708,41 @@
       <c r="G19" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="H19" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>42</v>
-      </c>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
       <c r="J19" s="9" t="s">
         <v>39</v>
       </c>
       <c r="K19" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="L19" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="M19" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="N19" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="O19" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="P19" s="8" t="s">
-        <v>38</v>
-      </c>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
       <c r="Q19" s="9" t="s">
         <v>40</v>
       </c>
       <c r="R19" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="S19" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="T19" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="U19" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="V19" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="W19" s="8" t="s">
-        <v>40</v>
-      </c>
+      <c r="S19" s="8"/>
+      <c r="T19" s="8"/>
+      <c r="U19" s="8"/>
+      <c r="V19" s="8"/>
+      <c r="W19" s="8"/>
       <c r="X19" s="9" t="s">
         <v>42</v>
       </c>
       <c r="Y19" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="Z19" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA19" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB19" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="AC19" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="AD19" s="8" t="s">
-        <v>39</v>
-      </c>
+      <c r="Z19" s="8"/>
+      <c r="AA19" s="8"/>
+      <c r="AB19" s="8"/>
+      <c r="AC19" s="8"/>
+      <c r="AD19" s="8"/>
       <c r="AE19" s="9" t="s">
         <v>41</v>
       </c>
@@ -2727,253 +2752,289 @@
     </row>
     <row r="20" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" s="8"/>
+        <v>43</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>41</v>
+      </c>
       <c r="C20" s="9" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>48</v>
+        <v>124</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>131</v>
+        <v>39</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
+        <v>40</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>42</v>
+      </c>
       <c r="J20" s="9" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8"/>
-      <c r="O20" s="8"/>
-      <c r="P20" s="8"/>
+        <v>41</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="M20" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="N20" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="O20" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="P20" s="8" t="s">
+        <v>38</v>
+      </c>
       <c r="Q20" s="9" t="s">
-        <v>131</v>
+        <v>40</v>
       </c>
       <c r="R20" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="S20" s="8"/>
-      <c r="T20" s="8"/>
-      <c r="U20" s="8"/>
-      <c r="V20" s="8"/>
-      <c r="W20" s="8"/>
+        <v>42</v>
+      </c>
+      <c r="S20" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="T20" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="U20" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="V20" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="W20" s="8" t="s">
+        <v>40</v>
+      </c>
       <c r="X20" s="9" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="Y20" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="Z20" s="8"/>
-      <c r="AA20" s="8"/>
-      <c r="AB20" s="8"/>
-      <c r="AC20" s="8"/>
-      <c r="AD20" s="8"/>
+        <v>38</v>
+      </c>
+      <c r="Z20" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA20" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB20" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="AC20" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AD20" s="8" t="s">
+        <v>39</v>
+      </c>
       <c r="AE20" s="9" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="AF20" s="9" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>48</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="B21" s="8"/>
       <c r="C21" s="9" t="s">
         <v>47</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>131</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="I21" s="8" t="s">
-        <v>49</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
       <c r="J21" s="9" t="s">
         <v>47</v>
       </c>
       <c r="K21" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="L21" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="M21" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="N21" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="O21" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="P21" s="8" t="s">
-        <v>47</v>
-      </c>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
       <c r="Q21" s="9" t="s">
         <v>131</v>
       </c>
       <c r="R21" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="S21" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="S21" s="8"/>
+      <c r="T21" s="8"/>
+      <c r="U21" s="8"/>
+      <c r="V21" s="8"/>
+      <c r="W21" s="8"/>
+      <c r="X21" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="T21" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="U21" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="V21" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="W21" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="X21" s="9" t="s">
-        <v>49</v>
-      </c>
       <c r="Y21" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z21" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA21" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB21" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="AC21" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="AD21" s="8" t="s">
-        <v>48</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="Z21" s="8"/>
+      <c r="AA21" s="8"/>
+      <c r="AB21" s="8"/>
+      <c r="AC21" s="8"/>
+      <c r="AD21" s="8"/>
       <c r="AE21" s="9" t="s">
         <v>47</v>
       </c>
       <c r="AF21" s="9" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B22" s="8"/>
+        <v>51</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>48</v>
+      </c>
       <c r="C22" s="9" t="s">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>125</v>
+        <v>52</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
+        <v>52</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>49</v>
+      </c>
       <c r="J22" s="9" t="s">
-        <v>136</v>
+        <v>47</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="L22" s="8"/>
-      <c r="M22" s="8"/>
-      <c r="N22" s="8"/>
-      <c r="O22" s="8"/>
-      <c r="P22" s="8"/>
+        <v>52</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="M22" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="N22" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="O22" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="P22" s="8" t="s">
+        <v>47</v>
+      </c>
       <c r="Q22" s="9" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="R22" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="S22" s="8"/>
-      <c r="T22" s="8"/>
-      <c r="U22" s="8"/>
-      <c r="V22" s="8"/>
-      <c r="W22" s="8"/>
+        <v>52</v>
+      </c>
+      <c r="S22" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="T22" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="U22" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="V22" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="W22" s="8" t="s">
+        <v>50</v>
+      </c>
       <c r="X22" s="9" t="s">
-        <v>146</v>
+        <v>49</v>
       </c>
       <c r="Y22" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="Z22" s="8"/>
-      <c r="AA22" s="8"/>
-      <c r="AB22" s="8"/>
-      <c r="AC22" s="8"/>
-      <c r="AD22" s="8"/>
+        <v>52</v>
+      </c>
+      <c r="Z22" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA22" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB22" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC22" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD22" s="8" t="s">
+        <v>48</v>
+      </c>
       <c r="AE22" s="9" t="s">
-        <v>150</v>
+        <v>47</v>
       </c>
       <c r="AF22" s="9" t="s">
-        <v>153</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
       <c r="J23" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K23" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L23" s="8"/>
       <c r="M23" s="8"/>
@@ -2981,10 +3042,10 @@
       <c r="O23" s="8"/>
       <c r="P23" s="8"/>
       <c r="Q23" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="R23" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="S23" s="8"/>
       <c r="T23" s="8"/>
@@ -2992,10 +3053,10 @@
       <c r="V23" s="8"/>
       <c r="W23" s="8"/>
       <c r="X23" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Y23" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Z23" s="8"/>
       <c r="AA23" s="8"/>
@@ -3003,277 +3064,275 @@
       <c r="AC23" s="8"/>
       <c r="AD23" s="8"/>
       <c r="AE23" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AF23" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="24" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>56</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B24" s="8"/>
       <c r="C24" s="9" t="s">
-        <v>57</v>
+        <v>123</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>58</v>
+        <v>129</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>59</v>
+        <v>133</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>62</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
       <c r="J24" s="9" t="s">
-        <v>63</v>
+        <v>137</v>
       </c>
       <c r="K24" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="L24" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="M24" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="N24" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="O24" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="P24" s="8" t="s">
-        <v>56</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
       <c r="Q24" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="R24" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="S24" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="T24" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="U24" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="V24" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="W24" s="8" t="s">
-        <v>73</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="S24" s="8"/>
+      <c r="T24" s="8"/>
+      <c r="U24" s="8"/>
+      <c r="V24" s="8"/>
+      <c r="W24" s="8"/>
       <c r="X24" s="9" t="s">
-        <v>68</v>
+        <v>147</v>
       </c>
       <c r="Y24" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z24" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA24" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="AB24" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC24" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD24" s="8" t="s">
-        <v>61</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="Z24" s="8"/>
+      <c r="AA24" s="8"/>
+      <c r="AB24" s="8"/>
+      <c r="AC24" s="8"/>
+      <c r="AD24" s="8"/>
       <c r="AE24" s="9" t="s">
-        <v>66</v>
+        <v>151</v>
       </c>
       <c r="AF24" s="9" t="s">
-        <v>60</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="7" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>79</v>
+        <v>127</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>134</v>
+        <v>59</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="K25" s="9" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="N25" s="8" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="O25" s="8" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="P25" s="8" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="Q25" s="9" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="R25" s="9" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="S25" s="8" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="T25" s="8" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="U25" s="8" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="V25" s="8" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="W25" s="8" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="X25" s="9" t="s">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="Y25" s="9" t="s">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="Z25" s="8" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="AA25" s="8" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="AB25" s="8" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="AC25" s="8" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="AD25" s="8" t="s">
-        <v>103</v>
+        <v>61</v>
       </c>
       <c r="AE25" s="9" t="s">
-        <v>104</v>
+        <v>66</v>
       </c>
       <c r="AF25" s="9" t="s">
-        <v>105</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="B26" s="8"/>
+        <v>76</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>77</v>
+      </c>
       <c r="C26" s="9" t="s">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
+        <v>80</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>82</v>
+      </c>
       <c r="J26" s="9" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="K26" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="L26" s="8"/>
-      <c r="M26" s="8"/>
-      <c r="N26" s="8"/>
-      <c r="O26" s="8"/>
-      <c r="P26" s="8"/>
+        <v>84</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="M26" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="N26" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="O26" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="P26" s="8" t="s">
+        <v>89</v>
+      </c>
       <c r="Q26" s="9" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="R26" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="S26" s="8"/>
-      <c r="T26" s="8"/>
-      <c r="U26" s="8"/>
-      <c r="V26" s="8"/>
-      <c r="W26" s="8"/>
+        <v>91</v>
+      </c>
+      <c r="S26" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="T26" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="U26" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="V26" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="W26" s="8" t="s">
+        <v>96</v>
+      </c>
       <c r="X26" s="9" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="Y26" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z26" s="8"/>
-      <c r="AA26" s="8"/>
-      <c r="AB26" s="8"/>
-      <c r="AC26" s="8"/>
-      <c r="AD26" s="8"/>
+        <v>98</v>
+      </c>
+      <c r="Z26" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA26" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB26" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC26" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="AD26" s="8" t="s">
+        <v>103</v>
+      </c>
       <c r="AE26" s="9" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="AF26" s="9" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>118</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="B27" s="8"/>
       <c r="C27" s="9" t="s">
         <v>107</v>
       </c>
@@ -3289,86 +3348,150 @@
       <c r="G27" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="H27" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="I27" s="8" t="s">
-        <v>114</v>
-      </c>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
       <c r="J27" s="9" t="s">
         <v>110</v>
       </c>
       <c r="K27" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="L27" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="M27" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="N27" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="O27" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="P27" s="8" t="s">
-        <v>108</v>
-      </c>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="8"/>
+      <c r="O27" s="8"/>
+      <c r="P27" s="8"/>
       <c r="Q27" s="9" t="s">
         <v>113</v>
       </c>
       <c r="R27" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="S27" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="T27" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="U27" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="V27" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="W27" s="8" t="s">
-        <v>109</v>
-      </c>
+      <c r="S27" s="8"/>
+      <c r="T27" s="8"/>
+      <c r="U27" s="8"/>
+      <c r="V27" s="8"/>
+      <c r="W27" s="8"/>
       <c r="X27" s="9" t="s">
         <v>114</v>
       </c>
       <c r="Y27" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="Z27" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA27" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="AB27" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="AC27" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD27" s="8" t="s">
-        <v>118</v>
-      </c>
+      <c r="Z27" s="8"/>
+      <c r="AA27" s="8"/>
+      <c r="AB27" s="8"/>
+      <c r="AC27" s="8"/>
+      <c r="AD27" s="8"/>
       <c r="AE27" s="9" t="s">
         <v>113</v>
       </c>
       <c r="AF27" s="9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="28" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M28" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="N28" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="O28" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="P28" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q28" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="R28" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="S28" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="T28" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="U28" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="V28" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="W28" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="X28" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y28" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z28" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA28" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB28" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="AC28" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD28" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AE28" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF28" s="9" t="s">
         <v>116</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:AF1"/>
-    <mergeCell ref="A17:AF17"/>
+    <mergeCell ref="A18:AF18"/>
   </mergeCells>
   <phoneticPr fontId="5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
